--- a/data/trans_dic/P20-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P20-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses</t>
+          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,79</t>
+          <t>1,52; 3,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,87; 8,91</t>
+          <t>4,87; 8,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,88; 7,22</t>
+          <t>3,66; 7,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,25; 9,3</t>
+          <t>5,22; 9,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,1; 9,11</t>
+          <t>5,06; 8,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,65; 13,54</t>
+          <t>8,45; 13,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,99; 9,08</t>
+          <t>5,04; 8,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,74; 7,94</t>
+          <t>4,87; 8,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,71; 5,93</t>
+          <t>3,68; 5,87</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,32; 10,45</t>
+          <t>7,45; 10,34</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,84; 7,56</t>
+          <t>4,88; 7,63</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,47; 8,06</t>
+          <t>5,4; 7,93</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 5,2</t>
+          <t>2,71; 5,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,69; 7,69</t>
+          <t>4,61; 7,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,28; 5,91</t>
+          <t>3,25; 5,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,17; 5,66</t>
+          <t>2,03; 5,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,08; 9,62</t>
+          <t>5,99; 9,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,58; 11,22</t>
+          <t>7,69; 11,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,84; 9,34</t>
+          <t>5,75; 9,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,24; 8,28</t>
+          <t>5,16; 8,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,79; 7,03</t>
+          <t>4,82; 7,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,58; 8,92</t>
+          <t>6,57; 9,07</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,07; 7,21</t>
+          <t>4,95; 7,06</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 6,4</t>
+          <t>3,33; 6,39</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,07; 7,72</t>
+          <t>3,99; 7,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,65; 8,56</t>
+          <t>4,58; 8,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,88; 6,23</t>
+          <t>2,91; 6,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,52; 6,83</t>
+          <t>3,61; 7,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,41; 10,54</t>
+          <t>6,56; 10,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,78; 11,98</t>
+          <t>7,67; 12,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,46; 9,21</t>
+          <t>5,36; 9,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,98</t>
+          <t>1,98; 5,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,75; 8,47</t>
+          <t>5,61; 8,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,67; 9,62</t>
+          <t>6,7; 9,67</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,61; 7,09</t>
+          <t>4,65; 7,07</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,91; 5,7</t>
+          <t>2,92; 5,74</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,39; 6,02</t>
+          <t>3,36; 5,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,31; 7,31</t>
+          <t>4,21; 7,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,93; 6,86</t>
+          <t>3,91; 6,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,18; 8,37</t>
+          <t>5,16; 8,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,29; 8,38</t>
+          <t>5,33; 8,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,02; 10,58</t>
+          <t>6,99; 10,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,44; 11,14</t>
+          <t>7,36; 11,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,18; 8,12</t>
+          <t>5,09; 8,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,65; 6,84</t>
+          <t>4,69; 6,79</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,0; 8,4</t>
+          <t>6,15; 8,4</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,99; 8,45</t>
+          <t>6,12; 8,5</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,52; 7,64</t>
+          <t>5,48; 7,63</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,49; 4,92</t>
+          <t>3,49; 4,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,29; 7,02</t>
+          <t>5,24; 6,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,08; 5,6</t>
+          <t>4,09; 5,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,3; 6,34</t>
+          <t>4,25; 6,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,57; 8,44</t>
+          <t>6,55; 8,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,54; 10,53</t>
+          <t>8,58; 10,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,82; 8,65</t>
+          <t>6,84; 8,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,86; 6,82</t>
+          <t>4,81; 6,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,26; 6,34</t>
+          <t>5,23; 6,37</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,18; 8,48</t>
+          <t>7,14; 8,51</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,72; 6,89</t>
+          <t>5,72; 6,93</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,9; 6,32</t>
+          <t>4,86; 6,3</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses</t>
+          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10357; 26261</t>
+          <t>10508; 26080</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>34285; 62655</t>
+          <t>34283; 61490</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26172; 48732</t>
+          <t>24676; 49753</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33347; 59076</t>
+          <t>33200; 58740</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>35127; 62692</t>
+          <t>34799; 60995</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>60273; 94349</t>
+          <t>58913; 93372</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33576; 61082</t>
+          <t>33892; 60019</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32031; 53676</t>
+          <t>32890; 55852</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>51308; 81850</t>
+          <t>50870; 81140</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>102505; 146358</t>
+          <t>104367; 144783</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65260; 101901</t>
+          <t>65754; 102852</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>71682; 105711</t>
+          <t>70813; 103926</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26230; 50052</t>
+          <t>26101; 49557</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47760; 78258</t>
+          <t>46906; 79275</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33490; 60424</t>
+          <t>33220; 60873</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25942; 67555</t>
+          <t>24193; 70284</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>58917; 93129</t>
+          <t>58026; 92493</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>78287; 115838</t>
+          <t>79340; 115913</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60929; 97423</t>
+          <t>59984; 96974</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>50220; 79375</t>
+          <t>49476; 80533</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>92533; 135669</t>
+          <t>92976; 136257</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>134886; 182916</t>
+          <t>134763; 185848</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>104791; 148908</t>
+          <t>102133; 145823</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>72875; 137663</t>
+          <t>71728; 137466</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>27641; 52370</t>
+          <t>27097; 52429</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35109; 64652</t>
+          <t>34574; 64471</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21868; 47336</t>
+          <t>22087; 48638</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24820; 48114</t>
+          <t>25456; 49316</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>43818; 72061</t>
+          <t>44836; 74099</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>60459; 93135</t>
+          <t>59615; 94481</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42892; 72284</t>
+          <t>42052; 72051</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20158; 55799</t>
+          <t>18507; 55650</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>78280; 115388</t>
+          <t>76454; 116067</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>102181; 147485</t>
+          <t>102749; 148191</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71162; 109559</t>
+          <t>71823; 109267</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>47640; 93306</t>
+          <t>47816; 94017</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>31982; 56724</t>
+          <t>31654; 55592</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40862; 69324</t>
+          <t>39942; 69682</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36867; 64331</t>
+          <t>36686; 63144</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48034; 77560</t>
+          <t>47816; 75086</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>54920; 87066</t>
+          <t>55307; 88071</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>73803; 111313</t>
+          <t>73562; 109409</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>77631; 116328</t>
+          <t>76800; 115393</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>56585; 88699</t>
+          <t>55568; 87963</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>92121; 135510</t>
+          <t>92964; 134465</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>119980; 168014</t>
+          <t>122898; 168006</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>118667; 167448</t>
+          <t>121240; 168424</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>111543; 154224</t>
+          <t>110584; 154075</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>114463; 161027</t>
+          <t>114249; 160390</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>181142; 240563</t>
+          <t>179576; 238955</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>138465; 190218</t>
+          <t>138742; 189650</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>148604; 219461</t>
+          <t>147065; 219115</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>221883; 285315</t>
+          <t>221283; 281499</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>304031; 374818</t>
+          <t>305250; 377915</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>241903; 306475</t>
+          <t>242355; 309016</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>177874; 249496</t>
+          <t>175872; 249986</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>350217; 422044</t>
+          <t>347926; 424115</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>501689; 591963</t>
+          <t>498597; 594004</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>396890; 477952</t>
+          <t>396945; 480834</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>348675; 450091</t>
+          <t>346082; 448675</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P20-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P20-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,76</t>
+          <t>1,52; 3,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,87; 8,74</t>
+          <t>4,85; 8,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,66; 7,37</t>
+          <t>3,79; 7,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,22; 9,24</t>
+          <t>5,2; 8,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,06; 8,86</t>
+          <t>5,27; 9,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,45; 13,4</t>
+          <t>8,7; 13,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,04; 8,92</t>
+          <t>4,98; 8,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,87; 8,27</t>
+          <t>4,98; 8,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,68; 5,87</t>
+          <t>3,75; 5,92</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,45; 10,34</t>
+          <t>7,17; 10,25</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,88; 7,63</t>
+          <t>5,03; 7,78</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,4; 7,93</t>
+          <t>5,53; 8,07</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,71; 5,15</t>
+          <t>2,79; 5,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,61; 7,79</t>
+          <t>4,68; 7,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,25; 5,95</t>
+          <t>3,22; 5,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 5,89</t>
+          <t>3,84; 7,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,99; 9,55</t>
+          <t>6,08; 9,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,69; 11,23</t>
+          <t>7,46; 11,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,75; 9,3</t>
+          <t>5,74; 9,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,16; 8,41</t>
+          <t>5,19; 8,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 7,06</t>
+          <t>4,83; 7,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,57; 9,07</t>
+          <t>6,47; 8,9</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,95; 7,06</t>
+          <t>4,91; 7,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,33; 6,39</t>
+          <t>5,0; 7,18</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,99; 7,73</t>
+          <t>4,07; 7,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,58; 8,53</t>
+          <t>4,56; 8,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,91; 6,4</t>
+          <t>2,89; 6,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,61; 7,0</t>
+          <t>3,36; 6,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,56; 10,84</t>
+          <t>6,47; 10,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,67; 12,16</t>
+          <t>7,75; 12,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,36; 9,18</t>
+          <t>5,53; 9,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 5,96</t>
+          <t>4,64; 8,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,61; 8,52</t>
+          <t>5,85; 8,61</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,7; 9,67</t>
+          <t>6,6; 9,62</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,65; 7,07</t>
+          <t>4,58; 7,03</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,92; 5,74</t>
+          <t>4,44; 6,64</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,36; 5,9</t>
+          <t>3,42; 6,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,21; 7,35</t>
+          <t>4,16; 7,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,91; 6,73</t>
+          <t>3,83; 6,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,16; 8,1</t>
+          <t>5,19; 8,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,33; 8,48</t>
+          <t>5,18; 8,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,99; 10,4</t>
+          <t>6,95; 10,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,36; 11,06</t>
+          <t>7,31; 10,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,09; 8,05</t>
+          <t>5,76; 8,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,69; 6,79</t>
+          <t>4,64; 6,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,15; 8,4</t>
+          <t>6,08; 8,3</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,12; 8,5</t>
+          <t>6,07; 8,54</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,48; 7,63</t>
+          <t>5,87; 7,83</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,49; 4,9</t>
+          <t>3,48; 4,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,24; 6,98</t>
+          <t>5,34; 7,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,09; 5,59</t>
+          <t>4,15; 5,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,25; 6,33</t>
+          <t>5,07; 6,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,55; 8,33</t>
+          <t>6,44; 8,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,58; 10,62</t>
+          <t>8,56; 10,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,84; 8,72</t>
+          <t>6,86; 8,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,81; 6,83</t>
+          <t>5,86; 7,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 6,37</t>
+          <t>5,19; 6,37</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,14; 8,51</t>
+          <t>7,18; 8,56</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,72; 6,93</t>
+          <t>5,7; 6,98</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,86; 6,3</t>
+          <t>5,66; 6,71</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44350</t>
+          <t>47921</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>42197</t>
+          <t>46899</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>86547</t>
+          <t>94819</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10508; 26080</t>
+          <t>10512; 26161</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>34283; 61490</t>
+          <t>34117; 60842</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24676; 49753</t>
+          <t>25552; 49002</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33200; 58740</t>
+          <t>35922; 61735</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>34799; 60995</t>
+          <t>36286; 63149</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>58913; 93372</t>
+          <t>60651; 94171</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33892; 60019</t>
+          <t>33537; 60038</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32890; 55852</t>
+          <t>36486; 60650</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>50870; 81140</t>
+          <t>51755; 81721</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>104367; 144783</t>
+          <t>100370; 143540</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65754; 102852</t>
+          <t>67742; 104808</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>70813; 103926</t>
+          <t>78699; 114878</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47488</t>
+          <t>54618</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>63352</t>
+          <t>69711</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>110840</t>
+          <t>124329</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26101; 49557</t>
+          <t>26860; 50946</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46906; 79275</t>
+          <t>47622; 78364</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33220; 60873</t>
+          <t>32963; 61235</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24193; 70284</t>
+          <t>40316; 73623</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>58026; 92493</t>
+          <t>58854; 93351</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>79340; 115913</t>
+          <t>77042; 116147</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59984; 96974</t>
+          <t>59835; 95736</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>49476; 80533</t>
+          <t>55629; 89167</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>92976; 136257</t>
+          <t>93141; 136362</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>134763; 185848</t>
+          <t>132737; 182559</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>102133; 145823</t>
+          <t>101355; 147420</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>71728; 137466</t>
+          <t>105999; 152173</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35389</t>
+          <t>38042</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38828</t>
+          <t>49748</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>74217</t>
+          <t>87790</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>27097; 52429</t>
+          <t>27621; 52824</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34574; 64471</t>
+          <t>34456; 65557</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22087; 48638</t>
+          <t>21948; 47645</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25456; 49316</t>
+          <t>27006; 50523</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>44836; 74099</t>
+          <t>44255; 71953</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>59615; 94481</t>
+          <t>60229; 93445</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42052; 72051</t>
+          <t>43416; 73080</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18507; 55650</t>
+          <t>37698; 65796</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>76454; 116067</t>
+          <t>79760; 117231</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>102749; 148191</t>
+          <t>101117; 147426</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71823; 109267</t>
+          <t>70761; 108577</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>47816; 94017</t>
+          <t>71700; 107208</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>60831</t>
+          <t>64598</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>72467</t>
+          <t>79110</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>133298</t>
+          <t>143708</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>31654; 55592</t>
+          <t>32268; 56735</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>39942; 69682</t>
+          <t>39397; 69253</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36686; 63144</t>
+          <t>35889; 63795</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47816; 75086</t>
+          <t>51406; 80486</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>55307; 88071</t>
+          <t>53825; 87041</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>73562; 109409</t>
+          <t>73153; 109642</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>76800; 115393</t>
+          <t>76266; 114587</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>55568; 87963</t>
+          <t>64448; 94246</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>92964; 134465</t>
+          <t>91928; 134668</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>122898; 168006</t>
+          <t>121625; 166001</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>121240; 168424</t>
+          <t>120305; 169144</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>110584; 154075</t>
+          <t>123709; 165006</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>188058</t>
+          <t>205178</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>216843</t>
+          <t>245467</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>404902</t>
+          <t>450645</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>114249; 160390</t>
+          <t>113852; 161439</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>179576; 238955</t>
+          <t>182917; 241405</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>138742; 189650</t>
+          <t>140882; 189532</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>147065; 219115</t>
+          <t>179132; 233033</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>221283; 281499</t>
+          <t>217521; 281291</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>305250; 377915</t>
+          <t>304653; 372775</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>242355; 309016</t>
+          <t>243318; 308758</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>175872; 249986</t>
+          <t>218887; 275599</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>347926; 424115</t>
+          <t>345434; 423699</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>498597; 594004</t>
+          <t>501056; 597539</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>396945; 480834</t>
+          <t>395829; 484261</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>346082; 448675</t>
+          <t>411442; 487883</t>
         </is>
       </c>
     </row>
